--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -38496,12 +38496,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -38541,75 +38541,94 @@
         <v>1</v>
       </c>
       <c r="R224" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -38636,17 +38655,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -38680,81 +38699,175 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O225" t="n">
-        <v>3</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Leptospirainfektion</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -38786,12 +38899,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -38816,7 +38929,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -38825,13 +38938,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -38864,42 +38977,42 @@
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -38931,12 +39044,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -38961,7 +39074,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -38970,93 +39083,81 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O227" t="n">
-        <v>1</v>
-      </c>
-      <c r="P227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R227" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39083,17 +39184,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -39127,173 +39228,81 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>1</v>
-      </c>
-      <c r="P228" t="n">
-        <v>1</v>
-      </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE228" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN228" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39325,12 +39334,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -39355,7 +39364,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -39369,76 +39378,88 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
+      <c r="P229" t="n">
+        <v>1</v>
+      </c>
       <c r="R229" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39465,17 +39486,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -39500,7 +39521,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -39514,76 +39535,168 @@
       <c r="O230" t="n">
         <v>1</v>
       </c>
-      <c r="R230" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P230" t="n">
+        <v>1</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39615,12 +39728,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -39645,7 +39758,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -39654,93 +39767,81 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
-      </c>
-      <c r="P231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39767,17 +39868,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -39811,173 +39912,81 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>0</v>
-      </c>
-      <c r="P232" t="n">
-        <v>0</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
         <v>1</v>
       </c>
+      <c r="R232" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40009,12 +40018,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -40039,7 +40048,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -40048,81 +40057,93 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40149,17 +40170,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -40184,7 +40205,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -40198,76 +40219,168 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="R234" t="n">
-        <v>0</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40299,12 +40412,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -40329,7 +40442,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -40343,88 +40456,76 @@
       <c r="O235" t="n">
         <v>1</v>
       </c>
-      <c r="P235" t="n">
-        <v>1</v>
-      </c>
       <c r="R235" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40451,17 +40552,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -40495,173 +40596,81 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>1</v>
-      </c>
-      <c r="P236" t="n">
-        <v>1</v>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN236" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40693,12 +40702,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -40723,7 +40732,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -40737,76 +40746,88 @@
       <c r="O237" t="n">
         <v>1</v>
       </c>
+      <c r="P237" t="n">
+        <v>1</v>
+      </c>
       <c r="R237" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40833,7 +40854,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -40868,7 +40889,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -40885,18 +40906,98 @@
       <c r="P238" t="n">
         <v>1</v>
       </c>
-      <c r="R238" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -40990,17 +41091,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -41039,168 +41140,76 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="P239" t="n">
-        <v>1</v>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN239" t="b">
-        <v>1</v>
+      <c r="R239" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41232,12 +41241,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -41262,90 +41271,102 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O240" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P240" t="n">
+        <v>1</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41372,17 +41393,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -41407,90 +41428,182 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O241" t="n">
-        <v>0</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P241" t="n">
+        <v>1</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN241" t="b">
+        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41522,12 +41635,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -41574,82 +41687,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -41676,212 +41775,516 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
+      <c r="F245" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="G245" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>D035</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
         <is>
           <t>钩端螺旋体病</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="K245" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="L245" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr">
+      <c r="M245" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N243" t="n">
-        <v>0</v>
-      </c>
-      <c r="O243" t="n">
-        <v>0</v>
-      </c>
-      <c r="U243" t="inlineStr">
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
+      <c r="V245" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="W243" t="inlineStr">
+      <c r="W245" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X243" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>Leptospirose</t>
         </is>
       </c>
-      <c r="Y243" t="inlineStr">
+      <c r="Y245" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr">
+      <c r="Z245" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA243" t="inlineStr">
+      <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB243" t="inlineStr">
+      <c r="AB245" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC243" t="inlineStr">
+      <c r="AC245" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD243" t="inlineStr">
+      <c r="AD245" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE243" t="inlineStr">
+      <c r="AE245" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF243" t="inlineStr">
+      <c r="AF245" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG243" t="inlineStr">
+      <c r="AG245" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH243" t="inlineStr">
+      <c r="AH245" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI243" t="inlineStr">
+      <c r="AI245" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ243" t="inlineStr">
+      <c r="AJ245" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK243" t="inlineStr">
+      <c r="AK245" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM243" t="inlineStr">
+      <c r="AM245" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN243" t="b">
+      <c r="AN245" t="b">
         <v>1</v>
       </c>
-      <c r="AO243" t="inlineStr">
+      <c r="AO245" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP243" t="inlineStr">
+      <c r="AP245" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ243" t="inlineStr">
+      <c r="AQ245" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS243" t="inlineStr">
+      <c r="AS245" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="AT243" t="n">
+      <c r="AT245" t="n">
         <v>1</v>
       </c>
-      <c r="AU243" t="inlineStr">
+      <c r="AU245" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV243" t="inlineStr">
+      <c r="AV245" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW243" t="inlineStr">
+      <c r="AW245" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX243" t="inlineStr">
+      <c r="AX245" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY243" t="inlineStr">
+      <c r="AY245" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ243" t="inlineStr">
+      <c r="AZ245" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA243" t="inlineStr">
+      <c r="BA245" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB243" t="inlineStr">
+      <c r="BB245" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC243" t="inlineStr">
+      <c r="BC245" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -42003,7 +42406,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -42013,7 +42416,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -42033,7 +42436,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -42065,7 +42468,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3049</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -37000,13 +37000,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R214" t="n">
-        <v>0.01101843545855937</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -41635,12 +41635,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N242" t="n">
@@ -41713,42 +41713,42 @@
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41780,12 +41780,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -41858,42 +41858,42 @@
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -41925,12 +41925,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -41977,82 +41977,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -42079,7 +42065,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -42128,98 +42114,23 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
+      <c r="R245" t="n">
+        <v>0</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U245" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
@@ -42285,6 +42196,240 @@
         </is>
       </c>
       <c r="BC245" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -42406,7 +42551,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -42416,7 +42561,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -42468,7 +42613,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3050</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -37000,13 +37000,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R214" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -41964,13 +41964,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3051</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -37000,13 +37000,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O214" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R214" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.02203687091711874</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -37958,12 +37958,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -37997,13 +37997,16 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>3</v>
+        <v>233</v>
       </c>
       <c r="O221" t="n">
-        <v>3</v>
+        <v>233</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.01649074079566728</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -38036,42 +38039,42 @@
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -38103,12 +38106,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -38142,95 +38145,81 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38257,7 +38246,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -38306,98 +38295,23 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U223" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG223" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM223" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN223" t="b">
-        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
@@ -38491,17 +38405,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -38535,100 +38449,170 @@
         </is>
       </c>
       <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
         <v>1</v>
       </c>
-      <c r="O224" t="n">
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
         <v>1</v>
       </c>
-      <c r="R224" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO224" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP224" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="AT224" t="n">
-        <v>2</v>
-      </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38655,7 +38639,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -38704,98 +38688,23 @@
       <c r="O225" t="n">
         <v>1</v>
       </c>
+      <c r="R225" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U225" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Leptospirainfektion</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
@@ -38894,17 +38803,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -38943,76 +38852,170 @@
       <c r="O226" t="n">
         <v>1</v>
       </c>
-      <c r="R226" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Leptospirainfektion</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39044,12 +39047,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -39083,13 +39086,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O227" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R227" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -39122,42 +39125,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -39189,12 +39192,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -39219,7 +39222,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -39228,13 +39231,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O228" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -39267,42 +39270,42 @@
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39334,12 +39337,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -39373,93 +39376,81 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>1</v>
-      </c>
-      <c r="P229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39486,7 +39477,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -39538,98 +39529,18 @@
       <c r="P230" t="n">
         <v>1</v>
       </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R230" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE230" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM230" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN230" t="b">
-        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
@@ -39723,17 +39634,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -39758,7 +39669,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -39772,76 +39683,168 @@
       <c r="O231" t="n">
         <v>1</v>
       </c>
-      <c r="R231" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P231" t="n">
+        <v>1</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39873,12 +39876,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -39903,7 +39906,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -39918,7 +39921,7 @@
         <v>1</v>
       </c>
       <c r="R232" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -39951,42 +39954,42 @@
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40018,12 +40021,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -40057,93 +40060,81 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
-      </c>
-      <c r="P233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40170,7 +40161,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -40222,98 +40213,18 @@
       <c r="P234" t="n">
         <v>0</v>
       </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG234" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM234" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN234" t="b">
-        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
@@ -40407,17 +40318,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -40442,7 +40353,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -40451,81 +40362,173 @@
         </is>
       </c>
       <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
         <v>1</v>
       </c>
-      <c r="O235" t="n">
-        <v>1</v>
-      </c>
-      <c r="R235" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40557,12 +40560,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -40587,7 +40590,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -40596,13 +40599,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -40635,42 +40638,42 @@
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40702,12 +40705,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -40741,93 +40744,81 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
-        <v>1</v>
-      </c>
-      <c r="P237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40854,7 +40845,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -40906,98 +40897,18 @@
       <c r="P238" t="n">
         <v>1</v>
       </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R238" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -41091,17 +41002,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -41126,7 +41037,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -41140,76 +41051,168 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="R239" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P239" t="n">
+        <v>1</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
+        <v>1</v>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41241,12 +41244,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -41285,88 +41288,76 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
-      <c r="P240" t="n">
-        <v>1</v>
-      </c>
       <c r="R240" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41393,7 +41384,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -41445,98 +41436,18 @@
       <c r="P241" t="n">
         <v>1</v>
       </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R241" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -41630,17 +41541,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -41665,7 +41576,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -41674,81 +41585,173 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P242" t="n">
+        <v>1</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41780,12 +41783,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -41810,12 +41813,12 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N243" t="n">
@@ -41858,42 +41861,42 @@
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41925,12 +41928,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -41955,90 +41958,102 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N244" t="n">
+        <v>4</v>
+      </c>
+      <c r="O244" t="n">
+        <v>4</v>
+      </c>
+      <c r="P244" t="n">
+        <v>4</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT244" t="n">
         <v>2</v>
       </c>
-      <c r="O244" t="n">
-        <v>2</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP244" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
-      <c r="AT244" t="n">
-        <v>0</v>
-      </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42065,17 +42080,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -42100,37 +42115,115 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P245" t="n">
+        <v>4</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
@@ -42139,7 +42232,7 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
@@ -42149,55 +42242,55 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42224,214 +42317,808 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>2</v>
+      </c>
+      <c r="O247" t="n">
+        <v>2</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
+      <c r="AT247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F249" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G249" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>D035</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
         <is>
           <t>钩端螺旋体病</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="K249" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
+      <c r="L249" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N246" t="n">
-        <v>0</v>
-      </c>
-      <c r="O246" t="n">
-        <v>0</v>
-      </c>
-      <c r="U246" t="inlineStr">
+      <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="U249" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V246" t="inlineStr">
+      <c r="V249" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="W246" t="inlineStr">
+      <c r="W249" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X246" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>Leptospirose</t>
         </is>
       </c>
-      <c r="Y246" t="inlineStr">
+      <c r="Y249" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z246" t="inlineStr">
+      <c r="Z249" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA246" t="inlineStr">
+      <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB246" t="inlineStr">
+      <c r="AB249" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC246" t="inlineStr">
+      <c r="AC249" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD246" t="inlineStr">
+      <c r="AD249" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE246" t="inlineStr">
+      <c r="AE249" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF246" t="inlineStr">
+      <c r="AF249" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG246" t="inlineStr">
+      <c r="AG249" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH246" t="inlineStr">
+      <c r="AH249" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI246" t="inlineStr">
+      <c r="AI249" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ246" t="inlineStr">
+      <c r="AJ249" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK246" t="inlineStr">
+      <c r="AK249" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM246" t="inlineStr">
+      <c r="AM249" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN246" t="b">
+      <c r="AN249" t="b">
         <v>1</v>
       </c>
-      <c r="AO246" t="inlineStr">
+      <c r="AO249" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP246" t="inlineStr">
+      <c r="AP249" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ246" t="inlineStr">
+      <c r="AQ249" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS246" t="inlineStr">
+      <c r="AS249" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="AT246" t="n">
+      <c r="AT249" t="n">
         <v>1</v>
       </c>
-      <c r="AU246" t="inlineStr">
+      <c r="AU249" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV246" t="inlineStr">
+      <c r="AV249" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW246" t="inlineStr">
+      <c r="AW249" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX246" t="inlineStr">
+      <c r="AX249" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY246" t="inlineStr">
+      <c r="AY249" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ246" t="inlineStr">
+      <c r="AZ249" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA246" t="inlineStr">
+      <c r="BA249" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB246" t="inlineStr">
+      <c r="BB249" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC246" t="inlineStr">
+      <c r="BC249" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>3</v>
+      </c>
+      <c r="O250" t="n">
+        <v>3</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr"/>
+      <c r="AT250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42468,7 +43155,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -42551,7 +43238,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -42561,7 +43248,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -42581,7 +43268,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -42613,7 +43300,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3054</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -43122,6 +43122,151 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>2</v>
+      </c>
+      <c r="O251" t="n">
+        <v>2</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43155,7 +43300,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -43238,7 +43383,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -43248,7 +43393,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -43300,7 +43445,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3295</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -33178,13 +33178,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O192" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R192" t="n">
-        <v>0.1891260466471829</v>
+        <v>0.1702134419824646</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -33337,10 +33337,10 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O193" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
@@ -38644,12 +38644,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -38683,100 +38683,95 @@
         </is>
       </c>
       <c r="N225" t="n">
+        <v>9</v>
+      </c>
+      <c r="O225" t="n">
+        <v>9</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0.1702134419824646</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT225" t="n">
         <v>1</v>
       </c>
-      <c r="O225" t="n">
-        <v>1</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="AA225" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP225" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="AT225" t="n">
-        <v>2</v>
-      </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38808,12 +38803,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -38847,29 +38842,29 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O226" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>Leptospirainfektion</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -38879,7 +38874,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -38894,7 +38889,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -38929,17 +38924,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly leptospirosis notifications.</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -38952,7 +38947,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -38960,62 +38955,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39047,12 +39037,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -39092,75 +39082,94 @@
         <v>1</v>
       </c>
       <c r="R227" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39187,17 +39196,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -39231,81 +39240,175 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O228" t="n">
-        <v>3</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Leptospirainfektion</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39337,12 +39440,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -39367,7 +39470,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -39376,13 +39479,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -39415,42 +39518,42 @@
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -39482,12 +39585,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -39512,7 +39615,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -39521,93 +39624,81 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O230" t="n">
-        <v>1</v>
-      </c>
-      <c r="P230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R230" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39634,17 +39725,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -39678,173 +39769,81 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
-        <v>1</v>
-      </c>
-      <c r="P231" t="n">
-        <v>1</v>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE231" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM231" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN231" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39876,12 +39875,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -39906,7 +39905,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -39920,76 +39919,88 @@
       <c r="O232" t="n">
         <v>1</v>
       </c>
+      <c r="P232" t="n">
+        <v>1</v>
+      </c>
       <c r="R232" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40016,17 +40027,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -40051,7 +40062,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -40065,76 +40076,168 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
-      <c r="R233" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P233" t="n">
+        <v>1</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40166,12 +40269,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -40196,7 +40299,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -40205,93 +40308,81 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O234" t="n">
-        <v>0</v>
-      </c>
-      <c r="P234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40318,17 +40409,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -40362,173 +40453,81 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
-        <v>0</v>
-      </c>
-      <c r="P235" t="n">
-        <v>0</v>
-      </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
         <v>1</v>
       </c>
+      <c r="R235" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40560,12 +40559,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -40590,7 +40589,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -40599,81 +40598,93 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40700,17 +40711,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -40735,7 +40746,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -40749,76 +40760,168 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="R237" t="n">
-        <v>0</v>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN237" t="b">
+        <v>1</v>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40850,12 +40953,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -40880,7 +40983,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -40894,88 +40997,76 @@
       <c r="O238" t="n">
         <v>1</v>
       </c>
-      <c r="P238" t="n">
-        <v>1</v>
-      </c>
       <c r="R238" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA238" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ238" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41002,17 +41093,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -41046,173 +41137,81 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
-        <v>1</v>
-      </c>
-      <c r="P239" t="n">
-        <v>1</v>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN239" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41244,12 +41243,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -41274,7 +41273,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -41288,76 +41287,88 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
+      <c r="P240" t="n">
+        <v>1</v>
+      </c>
       <c r="R240" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41384,7 +41395,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -41419,7 +41430,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -41436,18 +41447,98 @@
       <c r="P241" t="n">
         <v>1</v>
       </c>
-      <c r="R241" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN241" t="b">
+        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -41541,17 +41632,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -41590,168 +41681,76 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
-      <c r="P242" t="n">
-        <v>1</v>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W242" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE242" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG242" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ242" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK242" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM242" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN242" t="b">
-        <v>1</v>
+      <c r="R242" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41783,12 +41782,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -41813,7 +41812,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -41822,81 +41821,93 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P243" t="n">
+        <v>1</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41923,7 +41934,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -41958,7 +41969,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -41967,26 +41978,106 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O244" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P244" t="n">
-        <v>4</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.0677306302038819</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
@@ -42080,17 +42171,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -42124,173 +42215,81 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>4</v>
-      </c>
-      <c r="P245" t="n">
-        <v>4</v>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42322,12 +42321,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -42352,90 +42351,102 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O246" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P246" t="n">
+        <v>4</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>0.0677306302038819</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42462,17 +42473,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -42497,90 +42508,182 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N247" t="n">
+        <v>4</v>
+      </c>
+      <c r="O247" t="n">
+        <v>4</v>
+      </c>
+      <c r="P247" t="n">
+        <v>4</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT247" t="n">
         <v>2</v>
       </c>
-      <c r="O247" t="n">
-        <v>2</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO247" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP247" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
-      <c r="AT247" t="n">
-        <v>0</v>
-      </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42612,12 +42715,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -42664,82 +42767,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -42766,17 +42855,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -42810,170 +42899,81 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN249" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ249" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43005,12 +43005,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43035,7 +43035,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -43044,81 +43044,95 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43145,123 +43159,502 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>3</v>
+      </c>
+      <c r="O252" t="n">
+        <v>3</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
+      <c r="AT252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>D035</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
         <is>
           <t>钩端螺旋体病</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K253" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N251" t="n">
+      <c r="N253" t="n">
         <v>2</v>
       </c>
-      <c r="O251" t="n">
+      <c r="O253" t="n">
         <v>2</v>
       </c>
-      <c r="R251" t="n">
+      <c r="R253" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S251" t="inlineStr">
+      <c r="S253" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO251" t="inlineStr">
+      <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP251" t="inlineStr">
+      <c r="AP253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
+      <c r="AR253" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS251" t="inlineStr"/>
-      <c r="AT251" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU251" t="inlineStr">
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV251" t="inlineStr">
+      <c r="AV253" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW251" t="inlineStr">
+      <c r="AW253" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX251" t="inlineStr">
+      <c r="AX253" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY251" t="inlineStr">
+      <c r="AY253" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ251" t="inlineStr">
+      <c r="AZ253" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA251" t="inlineStr">
+      <c r="BA253" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB251" t="inlineStr">
+      <c r="BB253" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC251" t="inlineStr">
+      <c r="BC253" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -43383,7 +43776,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
@@ -43393,7 +43786,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -43413,7 +43806,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -43445,7 +43838,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3297</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -43660,6 +43660,545 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>2</v>
+      </c>
+      <c r="O254" t="n">
+        <v>2</v>
+      </c>
+      <c r="P254" t="n">
+        <v>2</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>2</v>
+      </c>
+      <c r="O255" t="n">
+        <v>2</v>
+      </c>
+      <c r="P255" t="n">
+        <v>2</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>2</v>
+      </c>
+      <c r="O256" t="n">
+        <v>2</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43693,7 +44232,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -43776,7 +44315,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -43786,7 +44325,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -43806,7 +44345,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -43838,7 +44377,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3305</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -31347,13 +31347,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O180" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R180" t="n">
-        <v>0.03305530637567811</v>
+        <v>0.0367281181951979</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -38106,12 +38106,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -38145,13 +38145,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R222" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -38184,42 +38184,42 @@
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -38251,12 +38251,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -38290,95 +38290,81 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38405,7 +38391,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -38454,98 +38440,23 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U224" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
@@ -38639,17 +38550,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -38683,22 +38594,39 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
-        <v>9</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.1702134419824646</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -38706,6 +38634,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38723,7 +38709,7 @@
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+          <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -38736,42 +38722,42 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38798,7 +38784,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -38847,98 +38833,23 @@
       <c r="O226" t="n">
         <v>9</v>
       </c>
+      <c r="R226" t="n">
+        <v>0.1702134419824646</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U226" t="inlineStr">
         <is>
           <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD226" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE226" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF226" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG226" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH226" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI226" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ226" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK226" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly leptospirosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM226" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN226" t="b">
-        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
@@ -39032,17 +38943,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -39076,100 +38987,170 @@
         </is>
       </c>
       <c r="N227" t="n">
+        <v>9</v>
+      </c>
+      <c r="O227" t="n">
+        <v>9</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly leptospirosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
         <v>1</v>
       </c>
-      <c r="O227" t="n">
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT227" t="n">
         <v>1</v>
       </c>
-      <c r="R227" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP227" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="AT227" t="n">
-        <v>2</v>
-      </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39196,7 +39177,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -39245,98 +39226,23 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
+      <c r="R228" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U228" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>Leptospirainfektion</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE228" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN228" t="b">
-        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
@@ -39435,17 +39341,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -39484,76 +39390,170 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
-      <c r="R229" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Leptospirainfektion</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39585,12 +39585,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -39624,13 +39624,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R230" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -39663,42 +39663,42 @@
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -39730,12 +39730,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -39760,7 +39760,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -39769,13 +39769,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -39808,42 +39808,42 @@
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39875,12 +39875,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -39914,93 +39914,81 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
-        <v>1</v>
-      </c>
-      <c r="P232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40027,7 +40015,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -40079,98 +40067,18 @@
       <c r="P233" t="n">
         <v>1</v>
       </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R233" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN233" t="b">
-        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
@@ -40264,17 +40172,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -40299,7 +40207,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -40313,76 +40221,168 @@
       <c r="O234" t="n">
         <v>1</v>
       </c>
-      <c r="R234" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P234" t="n">
+        <v>1</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40414,12 +40414,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -40444,7 +40444,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -40459,7 +40459,7 @@
         <v>1</v>
       </c>
       <c r="R235" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -40492,42 +40492,42 @@
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40559,12 +40559,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -40598,93 +40598,81 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>0</v>
-      </c>
-      <c r="P236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40711,7 +40699,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -40763,98 +40751,18 @@
       <c r="P237" t="n">
         <v>0</v>
       </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W237" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X237" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD237" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE237" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF237" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG237" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ237" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK237" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM237" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN237" t="b">
-        <v>1</v>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
@@ -40948,17 +40856,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -40983,7 +40891,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -40992,81 +40900,173 @@
         </is>
       </c>
       <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
         <v>1</v>
       </c>
-      <c r="O238" t="n">
-        <v>1</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41098,12 +41098,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -41128,7 +41128,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -41137,13 +41137,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -41176,42 +41176,42 @@
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41243,12 +41243,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -41282,93 +41282,81 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
-        <v>1</v>
-      </c>
-      <c r="P240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41395,7 +41383,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -41447,98 +41435,18 @@
       <c r="P241" t="n">
         <v>1</v>
       </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R241" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -41632,17 +41540,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -41667,7 +41575,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -41681,76 +41589,168 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
-      <c r="R242" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P242" t="n">
+        <v>1</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41782,12 +41782,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -41826,88 +41826,76 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
-      <c r="P243" t="n">
-        <v>1</v>
-      </c>
       <c r="R243" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41934,7 +41922,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -41986,98 +41974,18 @@
       <c r="P244" t="n">
         <v>1</v>
       </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R244" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
@@ -42171,17 +42079,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -42206,7 +42114,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -42215,81 +42123,173 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P245" t="n">
+        <v>1</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42321,12 +42321,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -42360,93 +42360,81 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
-        <v>4</v>
-      </c>
-      <c r="P246" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>0.0677306302038819</v>
+        <v>0</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42473,7 +42461,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -42525,98 +42513,18 @@
       <c r="P247" t="n">
         <v>4</v>
       </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R247" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN247" t="b">
-        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
@@ -42710,17 +42618,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -42745,90 +42653,182 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O248" t="n">
-        <v>0</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P248" t="n">
+        <v>4</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42860,12 +42860,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -42899,13 +42899,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -42938,42 +42938,42 @@
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -43005,12 +43005,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43044,95 +43044,81 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43159,7 +43145,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -43208,98 +43194,23 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U251" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
@@ -43393,17 +43304,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -43428,7 +43339,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -43437,81 +43348,170 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>3</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43543,12 +43543,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -43573,7 +43573,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -43582,13 +43582,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R253" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -43621,42 +43621,42 @@
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43688,12 +43688,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -43732,88 +43732,76 @@
       <c r="O254" t="n">
         <v>2</v>
       </c>
-      <c r="P254" t="n">
-        <v>2</v>
-      </c>
       <c r="R254" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43840,7 +43828,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -43892,98 +43880,18 @@
       <c r="P255" t="n">
         <v>2</v>
       </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R255" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
@@ -44077,17 +43985,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -44112,7 +44020,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -44126,74 +44034,995 @@
       <c r="O256" t="n">
         <v>2</v>
       </c>
-      <c r="R256" t="n">
+      <c r="P256" t="n">
+        <v>2</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>2</v>
+      </c>
+      <c r="O257" t="n">
+        <v>2</v>
+      </c>
+      <c r="R257" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S256" t="inlineStr">
+      <c r="S257" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO256" t="inlineStr">
+      <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP256" t="inlineStr">
+      <c r="AP257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR256" t="inlineStr">
+      <c r="AR257" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS256" t="inlineStr"/>
-      <c r="AT256" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU256" t="inlineStr">
+      <c r="AS257" t="inlineStr"/>
+      <c r="AT257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV256" t="inlineStr">
+      <c r="AV257" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW256" t="inlineStr">
+      <c r="AW257" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX256" t="inlineStr">
+      <c r="AX257" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY256" t="inlineStr">
+      <c r="AY257" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ256" t="inlineStr">
+      <c r="AZ257" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA256" t="inlineStr">
+      <c r="BA257" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB256" t="inlineStr">
+      <c r="BB257" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC256" t="inlineStr">
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>2</v>
+      </c>
+      <c r="O258" t="n">
+        <v>2</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
+      <c r="AT258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>4</v>
+      </c>
+      <c r="O259" t="n">
+        <v>4</v>
+      </c>
+      <c r="P259" t="n">
+        <v>4</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>4</v>
+      </c>
+      <c r="O260" t="n">
+        <v>4</v>
+      </c>
+      <c r="P260" t="n">
+        <v>4</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN260" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV260" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA260" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB260" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC260" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>6</v>
+      </c>
+      <c r="O261" t="n">
+        <v>6</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
+      <c r="AT261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -44232,7 +45061,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -44315,7 +45144,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -44325,7 +45154,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -44345,7 +45174,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -44377,7 +45206,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3309</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -45115,13 +45115,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O256" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R256" t="n">
-        <v>0.02203687091711874</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -53719,13 +53719,13 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R305" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
@@ -53864,13 +53864,13 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O306" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R306" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -55845,6 +55845,835 @@
       <c r="BC317" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>1</v>
+      </c>
+      <c r="O318" t="n">
+        <v>1</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr"/>
+      <c r="AT318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0</v>
+      </c>
+      <c r="P319" t="n">
+        <v>0</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>0</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
+      <c r="P320" t="n">
+        <v>0</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN320" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT320" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV320" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA320" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>1</v>
+      </c>
+      <c r="O321" t="n">
+        <v>1</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr"/>
+      <c r="AT321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>1</v>
+      </c>
+      <c r="O322" t="n">
+        <v>1</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr"/>
+      <c r="AT322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV322" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA322" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB322" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC322" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -55881,7 +56710,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -55964,7 +56793,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -55974,7 +56803,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11">
@@ -55994,7 +56823,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -56026,7 +56855,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3516</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -32168,7 +32168,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -49506,7 +49506,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -54260,7 +54260,7 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN308" t="b">
